--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N73_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N73_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.91534619758651</v>
+        <v>7.786243757107808</v>
       </c>
       <c r="D2" t="n">
-        <v>59.85509766134697</v>
+        <v>9.726453369968883</v>
       </c>
       <c r="E2" t="n">
-        <v>6.769296594885994</v>
+        <v>1.100010696668974</v>
       </c>
       <c r="F2" t="n">
-        <v>12.27617022745152</v>
+        <v>1.994877661960872</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>38.07129391553166</v>
+        <v>6.186585261273895</v>
       </c>
       <c r="D3" t="n">
-        <v>29.90241880632495</v>
+        <v>4.859143056027804</v>
       </c>
       <c r="E3" t="n">
-        <v>6.769296594885994</v>
+        <v>1.100010696668974</v>
       </c>
       <c r="F3" t="n">
-        <v>12.27617022745152</v>
+        <v>1.994877661960872</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.54867248537042</v>
+        <v>8.864159278872695</v>
       </c>
       <c r="D4" t="n">
-        <v>42.57715627083508</v>
+        <v>6.9187878940107</v>
       </c>
       <c r="E4" t="n">
-        <v>6.769296594885994</v>
+        <v>1.100010696668974</v>
       </c>
       <c r="F4" t="n">
-        <v>12.27617022745152</v>
+        <v>1.994877661960872</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
